--- a/workspaces/yzz100407/test_output/bills/商户账单_电费_2024-06.xlsx
+++ b/workspaces/yzz100407/test_output/bills/商户账单_电费_2024-06.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>星巴克咖啡</t>
+          <t>新名咖啡</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>异常</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
